--- a/megamillions_game.xlsx
+++ b/megamillions_game.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,56 +425,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>GameName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Num1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Num2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Num3</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Num4</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Num5</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MegaBall</t>
         </is>
@@ -3866,6 +3878,142 @@
       </c>
       <c r="J101" t="n">
         <v>24</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>6</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E102" t="n">
+        <v>15</v>
+      </c>
+      <c r="F102" t="n">
+        <v>26</v>
+      </c>
+      <c r="G102" t="n">
+        <v>43</v>
+      </c>
+      <c r="H102" t="n">
+        <v>48</v>
+      </c>
+      <c r="I102" t="n">
+        <v>60</v>
+      </c>
+      <c r="J102" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>5</v>
+      </c>
+      <c r="C103" t="n">
+        <v>29</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E103" t="n">
+        <v>19</v>
+      </c>
+      <c r="F103" t="n">
+        <v>24</v>
+      </c>
+      <c r="G103" t="n">
+        <v>47</v>
+      </c>
+      <c r="H103" t="n">
+        <v>59</v>
+      </c>
+      <c r="I103" t="n">
+        <v>65</v>
+      </c>
+      <c r="J103" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>5</v>
+      </c>
+      <c r="C104" t="n">
+        <v>26</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>49</v>
+      </c>
+      <c r="H104" t="n">
+        <v>51</v>
+      </c>
+      <c r="I104" t="n">
+        <v>59</v>
+      </c>
+      <c r="J104" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>6</v>
+      </c>
+      <c r="C105" t="n">
+        <v>5</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E105" t="n">
+        <v>13</v>
+      </c>
+      <c r="F105" t="n">
+        <v>30</v>
+      </c>
+      <c r="G105" t="n">
+        <v>50</v>
+      </c>
+      <c r="H105" t="n">
+        <v>52</v>
+      </c>
+      <c r="I105" t="n">
+        <v>66</v>
+      </c>
+      <c r="J105" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/megamillions_game.xlsx
+++ b/megamillions_game.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4016,6 +4016,40 @@
         <v>2</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>6</v>
+      </c>
+      <c r="C106" t="n">
+        <v>9</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E106" t="n">
+        <v>9</v>
+      </c>
+      <c r="F106" t="n">
+        <v>30</v>
+      </c>
+      <c r="G106" t="n">
+        <v>36</v>
+      </c>
+      <c r="H106" t="n">
+        <v>38</v>
+      </c>
+      <c r="I106" t="n">
+        <v>40</v>
+      </c>
+      <c r="J106" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/megamillions_game.xlsx
+++ b/megamillions_game.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4050,6 +4050,176 @@
         <v>3</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>6</v>
+      </c>
+      <c r="C107" t="n">
+        <v>26</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E107" t="n">
+        <v>5</v>
+      </c>
+      <c r="F107" t="n">
+        <v>13</v>
+      </c>
+      <c r="G107" t="n">
+        <v>30</v>
+      </c>
+      <c r="H107" t="n">
+        <v>33</v>
+      </c>
+      <c r="I107" t="n">
+        <v>52</v>
+      </c>
+      <c r="J107" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>6</v>
+      </c>
+      <c r="C108" t="n">
+        <v>23</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E108" t="n">
+        <v>48</v>
+      </c>
+      <c r="F108" t="n">
+        <v>51</v>
+      </c>
+      <c r="G108" t="n">
+        <v>60</v>
+      </c>
+      <c r="H108" t="n">
+        <v>63</v>
+      </c>
+      <c r="I108" t="n">
+        <v>66</v>
+      </c>
+      <c r="J108" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>6</v>
+      </c>
+      <c r="C109" t="n">
+        <v>19</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E109" t="n">
+        <v>13</v>
+      </c>
+      <c r="F109" t="n">
+        <v>16</v>
+      </c>
+      <c r="G109" t="n">
+        <v>21</v>
+      </c>
+      <c r="H109" t="n">
+        <v>26</v>
+      </c>
+      <c r="I109" t="n">
+        <v>50</v>
+      </c>
+      <c r="J109" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>6</v>
+      </c>
+      <c r="C110" t="n">
+        <v>16</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E110" t="n">
+        <v>12</v>
+      </c>
+      <c r="F110" t="n">
+        <v>20</v>
+      </c>
+      <c r="G110" t="n">
+        <v>53</v>
+      </c>
+      <c r="H110" t="n">
+        <v>67</v>
+      </c>
+      <c r="I110" t="n">
+        <v>70</v>
+      </c>
+      <c r="J110" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>6</v>
+      </c>
+      <c r="C111" t="n">
+        <v>12</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E111" t="n">
+        <v>9</v>
+      </c>
+      <c r="F111" t="n">
+        <v>17</v>
+      </c>
+      <c r="G111" t="n">
+        <v>24</v>
+      </c>
+      <c r="H111" t="n">
+        <v>39</v>
+      </c>
+      <c r="I111" t="n">
+        <v>51</v>
+      </c>
+      <c r="J111" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/megamillions_game.xlsx
+++ b/megamillions_game.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4220,6 +4220,278 @@
         <v>3</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>7</v>
+      </c>
+      <c r="C112" t="n">
+        <v>24</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>42</v>
+      </c>
+      <c r="H112" t="n">
+        <v>44</v>
+      </c>
+      <c r="I112" t="n">
+        <v>60</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>7</v>
+      </c>
+      <c r="C113" t="n">
+        <v>21</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E113" t="n">
+        <v>25</v>
+      </c>
+      <c r="F113" t="n">
+        <v>37</v>
+      </c>
+      <c r="G113" t="n">
+        <v>59</v>
+      </c>
+      <c r="H113" t="n">
+        <v>68</v>
+      </c>
+      <c r="I113" t="n">
+        <v>70</v>
+      </c>
+      <c r="J113" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>7</v>
+      </c>
+      <c r="C114" t="n">
+        <v>17</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E114" t="n">
+        <v>22</v>
+      </c>
+      <c r="F114" t="n">
+        <v>34</v>
+      </c>
+      <c r="G114" t="n">
+        <v>45</v>
+      </c>
+      <c r="H114" t="n">
+        <v>48</v>
+      </c>
+      <c r="I114" t="n">
+        <v>55</v>
+      </c>
+      <c r="J114" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>7</v>
+      </c>
+      <c r="C115" t="n">
+        <v>14</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" t="n">
+        <v>4</v>
+      </c>
+      <c r="G115" t="n">
+        <v>10</v>
+      </c>
+      <c r="H115" t="n">
+        <v>48</v>
+      </c>
+      <c r="I115" t="n">
+        <v>56</v>
+      </c>
+      <c r="J115" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>7</v>
+      </c>
+      <c r="C116" t="n">
+        <v>10</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2</v>
+      </c>
+      <c r="F116" t="n">
+        <v>39</v>
+      </c>
+      <c r="G116" t="n">
+        <v>44</v>
+      </c>
+      <c r="H116" t="n">
+        <v>46</v>
+      </c>
+      <c r="I116" t="n">
+        <v>56</v>
+      </c>
+      <c r="J116" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>7</v>
+      </c>
+      <c r="C117" t="n">
+        <v>7</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2</v>
+      </c>
+      <c r="F117" t="n">
+        <v>31</v>
+      </c>
+      <c r="G117" t="n">
+        <v>35</v>
+      </c>
+      <c r="H117" t="n">
+        <v>36</v>
+      </c>
+      <c r="I117" t="n">
+        <v>63</v>
+      </c>
+      <c r="J117" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>7</v>
+      </c>
+      <c r="C118" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E118" t="n">
+        <v>5</v>
+      </c>
+      <c r="F118" t="n">
+        <v>9</v>
+      </c>
+      <c r="G118" t="n">
+        <v>29</v>
+      </c>
+      <c r="H118" t="n">
+        <v>47</v>
+      </c>
+      <c r="I118" t="n">
+        <v>57</v>
+      </c>
+      <c r="J118" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Mega Millions</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>6</v>
+      </c>
+      <c r="C119" t="n">
+        <v>30</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E119" t="n">
+        <v>26</v>
+      </c>
+      <c r="F119" t="n">
+        <v>41</v>
+      </c>
+      <c r="G119" t="n">
+        <v>50</v>
+      </c>
+      <c r="H119" t="n">
+        <v>53</v>
+      </c>
+      <c r="I119" t="n">
+        <v>62</v>
+      </c>
+      <c r="J119" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
